--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>2771-366-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>104061.33</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2771-366-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10697.85</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="14">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>4886-60-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12890.69</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2409-608-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5391.65</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2409-646-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12400.79</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16061.33</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2416-187-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46631.79</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2416-186-CM26</t>
+          <t>2416-187-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>43355.11</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>2416-186-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9133.049999999999</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>43703.37</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2102-655-CM26</t>
+          <t>4886-97-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.343.454-0</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16587.73</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2408-724-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14179.41</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>2102-655-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.343.454-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>37143.95</v>
+        <v>16587.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057417-14604-CM26</t>
+          <t>2408-724-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3535.96</v>
+        <v>14179.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4081-278-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4385.96</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4358-167-CM26</t>
+          <t>1057417-14604-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3821.94</v>
+        <v>3535.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2408-777-CM26</t>
+          <t>4081-278-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10663.29</v>
+        <v>4385.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>4358-167-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,7 +2460,800 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>3821.94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2408-777-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>10663.29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1057417-15339-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>42076.74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1079576-942-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.954.400-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>6342.49</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1057627-19-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.607.101-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>12.382.191-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>3417.63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4081-301-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>14935.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>933-88-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3841.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>933-70-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>85024.07000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2409-1207-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.170.101-8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>10456.68</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>933-95-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>317.17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>654-323-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>27910.81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1057417-16197-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>22013.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1077367-61-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.301-k</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>41230.37</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3192-95-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.102.090-2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>4028.12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
@@ -1172,7 +1172,11 @@
           <t>77.498.695-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1603,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2644,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3014,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -575,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10699-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,12 +619,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +634,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34533.22</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,20 +688,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26393.09</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -745,20 +753,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>63924.39</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057417-10699-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,22 +810,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40321.27</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="7">
@@ -1002,7 +1018,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2102-387-CM26</t>
+          <t>2102-388-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1063,7 +1079,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2102-388-CM26</t>
+          <t>2102-387-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1481,7 +1497,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1494,7 +1514,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1514,17 +1534,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,28 +1554,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>861.54</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>4886-60-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1575,17 +1599,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,26 +1619,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>12.382.191-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12890.69</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="20">
@@ -2095,7 +2115,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2616,7 +2640,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2646,7 +2670,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2966,7 +2990,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>933-95-CM26</t>
+          <t>654-323-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2991,12 +3015,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,32 +3030,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>317.17</v>
+        <v>27910.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>654-323-CM26</t>
+          <t>933-95-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3056,12 +3076,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3071,28 +3091,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>27910.81</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057417-16197-CM26</t>
+          <t>1077367-61-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3117,7 +3141,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.301-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3147,13 +3171,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>22013.99</v>
+        <v>41230.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1077367-61-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3178,7 +3202,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.301-k</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3208,7 +3232,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41230.37</v>
+        <v>22013.99</v>
       </c>
     </row>
     <row r="46">
@@ -3270,6 +3294,315 @@
       </c>
       <c r="M46" s="2" t="n">
         <v>4028.12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1057627-22-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.607.101-7</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>12.382.191-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1043.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1417966-85-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>65.063.166-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN DESARROLLA BIOBÍO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CAROLYN MARLEN</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.905.851-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>20329.64</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2416-270-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CAROLYN MARLEN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.905.851-6</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1985.76</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1777-96-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.804.012-9</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>211983.43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057417-17061-SE26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>314520.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/biobio.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
